--- a/backend/src/utils/out.xlsx
+++ b/backend/src/utils/out.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <si>
     <t>WBS</t>
   </si>
@@ -459,6 +459,21 @@
   </si>
   <si>
     <t>ISSUE</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Test In Progress</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Độ ưu tiên</t>
   </si>
 </sst>
 </file>
@@ -1576,9 +1591,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/excel/2006/main" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{16B0ABBB-A333-4B32-A8E8-D2CE44EB3FF2}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="12.75" outlineLevelRow="1" ns3:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16B0ABBB-A333-4B32-A8E8-D2CE44EB3FF2}">
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultRowHeight="12.75" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="41" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.42578125" style="22" customWidth="1"/>
@@ -1595,7 +1610,7 @@
     <col min="13" max="16384" width="9.140625" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="25.5" ns3:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1629,131 +1644,87 @@
       <c r="K1" s="20" t="s">
         <v>114</v>
       </c>
+      <c r="L1" s="20" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="23">
-        <v>1</v>
-      </c>
-      <c r="B2" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
+      <c r="A2" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="C2" s="25"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="34"/>
+      <c r="D2" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="26">
+        <v>0.5</v>
+      </c>
       <c r="F2" s="27"/>
       <c r="G2" s="27"/>
       <c r="H2" s="28"/>
       <c r="I2" s="28"/>
       <c r="J2" s="29"/>
       <c r="K2" s="29"/>
+      <c r="L2" s="29" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B3" s="31" t="inlineStr">
-        <is>
-          <t>Test In Progress</t>
-        </is>
+      <c r="A3" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="25"/>
-      <c r="D3" s="42" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
+      <c r="D3" s="33" t="s">
+        <v>13</v>
       </c>
       <c r="E3" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
+        <v>1</v>
+      </c>
+      <c r="F3" s="27">
+        <v>46160.0</v>
+      </c>
+      <c r="G3" s="27">
+        <v>46162.0</v>
+      </c>
       <c r="H3" s="28"/>
       <c r="I3" s="28"/>
       <c r="J3" s="29"/>
       <c r="K3" s="29"/>
+      <c r="L3" s="29" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="23">
-        <v>2</v>
-      </c>
-      <c r="B4" s="24" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
+      <c r="A4" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>12</v>
       </c>
       <c r="C4" s="25"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="34"/>
+      <c r="D4" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="26">
+        <v>1</v>
+      </c>
       <c r="F4" s="27"/>
       <c r="G4" s="27"/>
-      <c r="H4" s="28"/>
+      <c r="H4" s="28">
+        <v>10</v>
+      </c>
       <c r="I4" s="28"/>
       <c r="J4" s="29"/>
       <c r="K4" s="29"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="30" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>OMNICHANNEL</t>
-        </is>
-      </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E5" s="26">
-        <v>1</v>
-      </c>
-      <c r="F5" s="27">
-        <v>46160.0</v>
-      </c>
-      <c r="G5" s="27">
-        <v>46162.0</v>
-      </c>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="33" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E6" s="26">
-        <v>1</v>
-      </c>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="28">
-        <v>10</v>
-      </c>
-      <c r="I6" s="28"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
+      <c r="L4" s="29" t="s">
+        <v>97</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="26" type="noConversion"/>
@@ -1782,8 +1753,8 @@
         <color rgb="FF638EC6"/>
       </dataBar>
       <extLst>
-        <ext uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <ns4:id>{ACB0C52E-E9C4-4E67-9130-E8396C657FCD}</ns4:id>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{ACB0C52E-E9C4-4E67-9130-E8396C657FCD}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1794,8 +1765,8 @@
         <color rgb="FF008AEF"/>
       </dataBar>
       <extLst>
-        <ext uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <ns4:id>{C4E8331A-2334-4338-A185-4AB10F643994}</ns4:id>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C4E8331A-2334-4338-A185-4AB10F643994}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1806,8 +1777,8 @@
         <color rgb="FF63C384"/>
       </dataBar>
       <extLst>
-        <ext uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <ns4:id>{15291FFA-D9CB-46FD-B656-392F6CC42731}</ns4:id>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{15291FFA-D9CB-46FD-B656-392F6CC42731}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1818,8 +1789,8 @@
         <color rgb="FFFF555A"/>
       </dataBar>
       <extLst>
-        <ext uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <ns4:id>{0B06D3C3-1B5D-4FA5-AD88-1D43A3F12834}</ns4:id>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0B06D3C3-1B5D-4FA5-AD88-1D43A3F12834}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1830,8 +1801,8 @@
         <color rgb="FF008AEF"/>
       </dataBar>
       <extLst>
-        <ext uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <ns4:id>{909D4B96-A169-4CE9-B437-CBEFF4A5001E}</ns4:id>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{909D4B96-A169-4CE9-B437-CBEFF4A5001E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1842,8 +1813,8 @@
         <color rgb="FF638EC6"/>
       </dataBar>
       <extLst>
-        <ext uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <ns4:id>{4E5F2654-6D89-4E38-82F4-C15B1E261236}</ns4:id>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{4E5F2654-6D89-4E38-82F4-C15B1E261236}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1854,8 +1825,8 @@
         <color rgb="FF638EC6"/>
       </dataBar>
       <extLst>
-        <ext uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <ns4:id>{9CD694C6-E363-4464-B2B8-60591B4FD796}</ns4:id>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9CD694C6-E363-4464-B2B8-60591B4FD796}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1868,8 +1839,8 @@
         <color rgb="FF638EC6"/>
       </dataBar>
       <extLst>
-        <ext uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <ns4:id>{E83DE19E-9F72-4614-A0E5-E5841E54B32C}</ns4:id>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E83DE19E-9F72-4614-A0E5-E5841E54B32C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1882,8 +1853,8 @@
         <color rgb="FF638EC6"/>
       </dataBar>
       <extLst>
-        <ext uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <ns4:id>{23B5A057-D322-48BE-ADAB-29616FF926E2}</ns4:id>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{23B5A057-D322-48BE-ADAB-29616FF926E2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1910,114 +1881,114 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
-    <ext uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <ns4:conditionalFormattings>
-        <ns4:conditionalFormatting>
-          <ns4:cfRule type="dataBar" id="{ACB0C52E-E9C4-4E67-9130-E8396C657FCD}">
-            <ns4:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <ns4:cfvo type="autoMin"/>
-              <ns4:cfvo type="autoMax"/>
-              <ns4:borderColor rgb="FF638EC6"/>
-              <ns4:negativeFillColor rgb="FFFF0000"/>
-              <ns4:negativeBorderColor rgb="FFFF0000"/>
-              <ns4:axisColor rgb="FF000000"/>
-            </ns4:dataBar>
-          </ns4:cfRule>
-          <ns4:cfRule type="dataBar" id="{C4E8331A-2334-4338-A185-4AB10F643994}">
-            <ns4:dataBar minLength="0" maxLength="100" gradient="0">
-              <ns4:cfvo type="autoMin"/>
-              <ns4:cfvo type="autoMax"/>
-              <ns4:negativeFillColor rgb="FFFF0000"/>
-              <ns4:axisColor rgb="FF000000"/>
-            </ns4:dataBar>
-          </ns4:cfRule>
-          <ns4:cfRule type="dataBar" id="{15291FFA-D9CB-46FD-B656-392F6CC42731}">
-            <ns4:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <ns4:cfvo type="autoMin"/>
-              <ns4:cfvo type="autoMax"/>
-              <ns4:borderColor rgb="FF63C384"/>
-              <ns4:negativeFillColor rgb="FFFF0000"/>
-              <ns4:negativeBorderColor rgb="FFFF0000"/>
-              <ns4:axisColor rgb="FF000000"/>
-            </ns4:dataBar>
-          </ns4:cfRule>
-          <ns4:cfRule type="dataBar" id="{0B06D3C3-1B5D-4FA5-AD88-1D43A3F12834}">
-            <ns4:dataBar minLength="0" maxLength="100" gradient="0">
-              <ns4:cfvo type="autoMin"/>
-              <ns4:cfvo type="autoMax"/>
-              <ns4:negativeFillColor rgb="FFFF0000"/>
-              <ns4:axisColor rgb="FF000000"/>
-            </ns4:dataBar>
-          </ns4:cfRule>
-          <ns4:cfRule type="dataBar" id="{909D4B96-A169-4CE9-B437-CBEFF4A5001E}">
-            <ns4:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <ns4:cfvo type="autoMin"/>
-              <ns4:cfvo type="autoMax"/>
-              <ns4:borderColor rgb="FF008AEF"/>
-              <ns4:negativeFillColor rgb="FFFF0000"/>
-              <ns4:negativeBorderColor rgb="FFFF0000"/>
-              <ns4:axisColor rgb="FF000000"/>
-            </ns4:dataBar>
-          </ns4:cfRule>
-          <ns4:cfRule type="dataBar" id="{4E5F2654-6D89-4E38-82F4-C15B1E261236}">
-            <ns4:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <ns4:cfvo type="autoMin"/>
-              <ns4:cfvo type="autoMax"/>
-              <ns4:borderColor rgb="FF638EC6"/>
-              <ns4:negativeFillColor rgb="FFFF0000"/>
-              <ns4:negativeBorderColor rgb="FFFF0000"/>
-              <ns4:axisColor rgb="FF000000"/>
-            </ns4:dataBar>
-          </ns4:cfRule>
-          <ns4:cfRule type="dataBar" id="{9CD694C6-E363-4464-B2B8-60591B4FD796}">
-            <ns4:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <ns4:cfvo type="autoMin"/>
-              <ns4:cfvo type="autoMax"/>
-              <ns4:borderColor rgb="FF638EC6"/>
-              <ns4:negativeFillColor rgb="FFFF0000"/>
-              <ns4:negativeBorderColor rgb="FFFF0000"/>
-              <ns4:axisColor rgb="FF000000"/>
-            </ns4:dataBar>
-          </ns4:cfRule>
-          <ns5:sqref>E1</ns5:sqref>
-        </ns4:conditionalFormatting>
-        <ns4:conditionalFormatting>
-          <ns4:cfRule type="dataBar" id="{E83DE19E-9F72-4614-A0E5-E5841E54B32C}">
-            <ns4:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <ns4:cfvo type="autoMin"/>
-              <ns4:cfvo type="autoMax"/>
-              <ns4:borderColor rgb="FF638EC6"/>
-              <ns4:negativeFillColor rgb="FFFF0000"/>
-              <ns4:negativeBorderColor rgb="FFFF0000"/>
-              <ns4:axisColor rgb="FF000000"/>
-            </ns4:dataBar>
-          </ns4:cfRule>
-          <ns5:sqref>E2:E11</ns5:sqref>
-        </ns4:conditionalFormatting>
-        <ns4:conditionalFormatting>
-          <ns4:cfRule type="dataBar" id="{23B5A057-D322-48BE-ADAB-29616FF926E2}">
-            <ns4:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <ns4:cfvo type="autoMin"/>
-              <ns4:cfvo type="autoMax"/>
-              <ns4:borderColor rgb="FF638EC6"/>
-              <ns4:negativeFillColor rgb="FFFF0000"/>
-              <ns4:negativeBorderColor rgb="FFFF0000"/>
-              <ns4:axisColor rgb="FF000000"/>
-            </ns4:dataBar>
-          </ns4:cfRule>
-          <ns5:sqref>E12:E22</ns5:sqref>
-        </ns4:conditionalFormatting>
-      </ns4:conditionalFormattings>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{ACB0C52E-E9C4-4E67-9130-E8396C657FCD}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{C4E8331A-2334-4338-A185-4AB10F643994}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{15291FFA-D9CB-46FD-B656-392F6CC42731}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{0B06D3C3-1B5D-4FA5-AD88-1D43A3F12834}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{909D4B96-A169-4CE9-B437-CBEFF4A5001E}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF008AEF"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{4E5F2654-6D89-4E38-82F4-C15B1E261236}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{9CD694C6-E363-4464-B2B8-60591B4FD796}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E1</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{E83DE19E-9F72-4614-A0E5-E5841E54B32C}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E2:E11</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{23B5A057-D322-48BE-ADAB-29616FF926E2}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E12:E22</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
     </ext>
-    <ext uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <ns4:dataValidations count="1">
-        <ns4:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" ns2:uid="{9C8B68F4-1F93-4A76-ADC2-C64198651A1B}">
-          <ns4:formula1>
-            <ns5:f>Status!$A$1:$A$10</ns5:f>
-          </ns4:formula1>
-          <ns5:sqref>D2:D1048576</ns5:sqref>
-        </ns4:dataValidation>
-      </ns4:dataValidations>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9C8B68F4-1F93-4A76-ADC2-C64198651A1B}">
+          <x14:formula1>
+            <xm:f>Status!$A$1:$A$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
     </ext>
   </extLst>
 </worksheet>
